--- a/artfynd/A 33564-2026 artfynd.xlsx
+++ b/artfynd/A 33564-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131033116</v>
+        <v>135942928</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hykjeberg söder, Dlr</t>
+          <t>Klittmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458032</v>
+        <v>458377</v>
       </c>
       <c r="R2" t="n">
-        <v>6792590</v>
+        <v>6792404</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,49 +775,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131033116</t>
+          <t>https://artportalen.se/Sighting/135942928</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131033114</v>
+        <v>131033116</v>
       </c>
       <c r="B3" t="n">
-        <v>92083</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457975</v>
+        <v>458032</v>
       </c>
       <c r="R3" t="n">
-        <v>6792558</v>
+        <v>6792590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,54 +888,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131033114</t>
+          <t>https://artportalen.se/Sighting/131033116</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131033122</v>
+        <v>135942926</v>
       </c>
       <c r="B4" t="n">
-        <v>92083</v>
+        <v>79107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hykjeberg söder, Dlr</t>
+          <t>Klittmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457838</v>
+        <v>458353</v>
       </c>
       <c r="R4" t="n">
-        <v>6792453</v>
+        <v>6792435</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +959,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +989,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131033122</t>
+          <t>https://artportalen.se/Sighting/135942926</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131033119</v>
+        <v>135942931</v>
       </c>
       <c r="B5" t="n">
-        <v>93197</v>
+        <v>79107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hykjeberg söder, Dlr</t>
+          <t>Klittmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458139</v>
+        <v>458367</v>
       </c>
       <c r="R5" t="n">
-        <v>6792679</v>
+        <v>6792350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1071,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,68 +1101,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131033119</t>
+          <t>https://artportalen.se/Sighting/135942931</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135005351</v>
+        <v>131033114</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hykjeberg , Dlr</t>
+          <t>Hykjeberg söder, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458098</v>
+        <v>457975</v>
       </c>
       <c r="R6" t="n">
-        <v>6792582</v>
+        <v>6792558</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,12 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,34 +1197,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135005351</t>
+          <t>https://artportalen.se/Sighting/131033114</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131033115</v>
+        <v>131033122</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457976</v>
+        <v>457838</v>
       </c>
       <c r="R7" t="n">
-        <v>6792593</v>
+        <v>6792453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,54 +1316,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131033115</t>
+          <t>https://artportalen.se/Sighting/131033122</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135445722</v>
+        <v>131033119</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hykjeberg, Dlr</t>
+          <t>Hykjeberg söder, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457768</v>
+        <v>458139</v>
       </c>
       <c r="R8" t="n">
-        <v>6792314</v>
+        <v>6792679</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,12 +1387,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1378,34 +1401,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445722</t>
+          <t>https://artportalen.se/Sighting/131033119</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135012547</v>
+        <v>135005351</v>
       </c>
       <c r="B9" t="n">
-        <v>78841</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1440,13 +1462,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458118</v>
+        <v>458098</v>
       </c>
       <c r="R9" t="n">
-        <v>6792550</v>
+        <v>6792582</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,54 +1524,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135012547</t>
+          <t>https://artportalen.se/Sighting/135005351</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135445426</v>
+        <v>131033115</v>
       </c>
       <c r="B10" t="n">
-        <v>79198</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hykjeberg, Dlr</t>
+          <t>Hykjeberg söder, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457796</v>
+        <v>457976</v>
       </c>
       <c r="R10" t="n">
-        <v>6792277</v>
+        <v>6792593</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,12 +1595,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,69 +1609,71 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445426</t>
+          <t>https://artportalen.se/Sighting/131033115</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131033118</v>
+        <v>135445722</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>79441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hykjeberg söder, Dlr</t>
+          <t>Hykjeberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458120</v>
+        <v>457768</v>
       </c>
       <c r="R11" t="n">
-        <v>6792626</v>
+        <v>6792314</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,12 +1700,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,71 +1714,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Filip Ragnarsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Filip Ragnarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131033118</t>
+          <t>https://artportalen.se/Sighting/135445722</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131033123</v>
+        <v>135942932</v>
       </c>
       <c r="B12" t="n">
-        <v>79085</v>
+        <v>79441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hykjeberg söder, Dlr</t>
+          <t>Klittmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457734</v>
+        <v>458389</v>
       </c>
       <c r="R12" t="n">
-        <v>6792504</v>
+        <v>6792348</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1781,12 +1803,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1801,68 +1833,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131033123</t>
+          <t>https://artportalen.se/Sighting/135942932</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135445420</v>
+        <v>135942933</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>79441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hykjeberg, Dlr</t>
+          <t>Klittmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457768</v>
+        <v>458389</v>
       </c>
       <c r="R13" t="n">
-        <v>6792314</v>
+        <v>6792336</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1886,12 +1915,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1900,23 +1939,3156 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942933</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135942935</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>458424</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6792308</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942935</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135942941</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>458326</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6792433</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942941</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135942949</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>458296</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6792402</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942949</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135942951</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>458254</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6792464</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942951</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135942952</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>458269</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6792474</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942952</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135945181</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>458319</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6792448</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135945181</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135945183</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>458304</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6792449</v>
+      </c>
+      <c r="S20" t="n">
+        <v>7</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135945183</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135012547</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hykjeberg , Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>458118</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6792550</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Filip Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Filip Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135012547</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135445426</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hykjeberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>457796</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6792277</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Filip Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Filip Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445426</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135942929</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>458378</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6792406</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942929</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135942930</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>458361</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6792340</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942930</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131033118</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hykjeberg söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>458120</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6792626</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033118</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135942927</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>458353</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6792435</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942927</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135942938</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>458417</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6792261</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942938</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135942943</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>458305</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6792436</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942943</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135942947</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>458288</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6792419</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942947</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135945187</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>458265</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6792434</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135945187</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135942948</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>458287</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6792413</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942948</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135942946</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58601</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>458272</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6792433</v>
+      </c>
+      <c r="S32" t="n">
+        <v>7</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942946</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135942934</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>458408</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6792311</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942934</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135942937</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>458418</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6792258</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942937</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135942944</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>458301</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6792433</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942944</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135945185</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>458265</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6792434</v>
+      </c>
+      <c r="S36" t="n">
+        <v>9</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135945185</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135942942</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>458309</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6792448</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist, Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942942</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135945182</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Klittmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>458307</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6792449</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135945182</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131033123</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hykjeberg söder, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>457734</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6792504</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033123</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135445420</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hykjeberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>457768</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6792314</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Filip Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Filip Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135445420</t>
         </is>
@@ -1936,6 +5108,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33564-2026 artfynd.xlsx
+++ b/artfynd/A 33564-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4031,35 +4031,39 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135942946</v>
+        <v>136007050</v>
       </c>
       <c r="B32" t="n">
-        <v>58601</v>
+        <v>58141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103041</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -4071,13 +4075,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458272</v>
+        <v>457953</v>
       </c>
       <c r="R32" t="n">
-        <v>6792433</v>
+        <v>6792218</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4101,22 +4105,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4131,27 +4135,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135942946</t>
+          <t>https://artportalen.se/Sighting/136007050</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135942934</v>
+        <v>135942946</v>
       </c>
       <c r="B33" t="n">
-        <v>8461</v>
+        <v>58601</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4159,27 +4163,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>103041</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4188,13 +4192,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458408</v>
+        <v>458272</v>
       </c>
       <c r="R33" t="n">
-        <v>6792311</v>
+        <v>6792433</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4223,7 +4227,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4233,7 +4237,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,13 +4263,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135942934</t>
+          <t>https://artportalen.se/Sighting/135942946</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135942937</v>
+        <v>135942934</v>
       </c>
       <c r="B34" t="n">
         <v>8461</v>
@@ -4305,13 +4309,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458418</v>
+        <v>458408</v>
       </c>
       <c r="R34" t="n">
-        <v>6792258</v>
+        <v>6792311</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4340,7 +4344,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4350,7 +4354,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,13 +4380,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135942937</t>
+          <t>https://artportalen.se/Sighting/135942934</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135942944</v>
+        <v>135942937</v>
       </c>
       <c r="B35" t="n">
         <v>8461</v>
@@ -4422,13 +4426,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458301</v>
+        <v>458418</v>
       </c>
       <c r="R35" t="n">
-        <v>6792433</v>
+        <v>6792258</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4457,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4478,26 +4482,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4513,13 +4497,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135942944</t>
+          <t>https://artportalen.se/Sighting/135942937</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135945185</v>
+        <v>135942944</v>
       </c>
       <c r="B36" t="n">
         <v>8461</v>
@@ -4559,13 +4543,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458265</v>
+        <v>458301</v>
       </c>
       <c r="R36" t="n">
-        <v>6792434</v>
+        <v>6792433</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4594,7 +4578,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4604,7 +4588,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4616,6 +4600,16 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM36" t="inlineStr">
         <is>
           <t>Stående död trädstam/högstubbe</t>
@@ -4623,65 +4617,61 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945185</t>
+          <t>https://artportalen.se/Sighting/135942944</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135942942</v>
+        <v>135945185</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>8461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4690,13 +4680,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>458309</v>
+        <v>458265</v>
       </c>
       <c r="R37" t="n">
-        <v>6792448</v>
+        <v>6792434</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4725,7 +4715,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4735,7 +4725,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4746,28 +4736,38 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135942942</t>
+          <t>https://artportalen.se/Sighting/135945185</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135945182</v>
+        <v>135942942</v>
       </c>
       <c r="B38" t="n">
         <v>99276</v>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4811,13 +4811,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>458307</v>
+        <v>458309</v>
       </c>
       <c r="R38" t="n">
-        <v>6792449</v>
+        <v>6792448</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4871,65 +4871,74 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945182</t>
+          <t>https://artportalen.se/Sighting/135942942</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131033123</v>
+        <v>135945182</v>
       </c>
       <c r="B39" t="n">
-        <v>79085</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hykjeberg söder, Dlr</t>
+          <t>Klittmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457734</v>
+        <v>458307</v>
       </c>
       <c r="R39" t="n">
-        <v>6792504</v>
+        <v>6792449</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4953,12 +4962,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4973,27 +4992,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131033123</t>
+          <t>https://artportalen.se/Sighting/135945182</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135445420</v>
+        <v>131033123</v>
       </c>
       <c r="B40" t="n">
-        <v>79199</v>
+        <v>79085</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,19 +5038,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hykjeberg, Dlr</t>
+          <t>Hykjeberg söder, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457768</v>
+        <v>457734</v>
       </c>
       <c r="R40" t="n">
-        <v>6792314</v>
+        <v>6792504</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5058,12 +5074,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5072,23 +5088,128 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Filip Ragnarsson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131033123</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135445420</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hykjeberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>457768</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6792314</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Filip Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Filip Ragnarsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135445420</t>
         </is>
@@ -5135,6 +5256,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33564-2026 artfynd.xlsx
+++ b/artfynd/A 33564-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135942928</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135942926</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135942931</v>
       </c>
       <c r="B5" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135445722</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>135942932</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135942933</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>135942935</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135942941</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>135942949</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135942951</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>135942952</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>135945181</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>135945183</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>135445426</v>
       </c>
       <c r="B22" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>135942929</v>
       </c>
       <c r="B23" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>135942930</v>
       </c>
       <c r="B24" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>135942927</v>
       </c>
       <c r="B26" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>135942938</v>
       </c>
       <c r="B27" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>135942943</v>
       </c>
       <c r="B28" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135942947</v>
       </c>
       <c r="B29" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>135945187</v>
       </c>
       <c r="B30" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>135942948</v>
       </c>
       <c r="B31" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136007050</v>
       </c>
       <c r="B32" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135942946</v>
       </c>
       <c r="B33" t="n">
-        <v>58601</v>
+        <v>58603</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135942934</v>
       </c>
       <c r="B34" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>135942937</v>
       </c>
       <c r="B35" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>135942944</v>
       </c>
       <c r="B36" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>135945185</v>
       </c>
       <c r="B37" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>135942942</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>135945182</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>135445420</v>
       </c>
       <c r="B41" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 33564-2026 artfynd.xlsx
+++ b/artfynd/A 33564-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135942928</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135942926</v>
       </c>
       <c r="B4" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135942931</v>
       </c>
       <c r="B5" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>135942932</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135942933</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>135942935</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135942941</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>135942949</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135942951</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>135942952</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>135945181</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>135945183</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>135942929</v>
       </c>
       <c r="B23" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>135942930</v>
       </c>
       <c r="B24" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>135942927</v>
       </c>
       <c r="B26" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>135942942</v>
       </c>
       <c r="B38" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>135945182</v>
       </c>
       <c r="B39" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 33564-2026 artfynd.xlsx
+++ b/artfynd/A 33564-2026 artfynd.xlsx
@@ -4770,7 +4770,7 @@
         <v>135942942</v>
       </c>
       <c r="B38" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>135945182</v>
       </c>
       <c r="B39" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 33564-2026 artfynd.xlsx
+++ b/artfynd/A 33564-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135942928</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135942926</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135942931</v>
       </c>
       <c r="B5" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>135942932</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135942933</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>135942935</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135942941</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>135942949</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135942951</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>135942952</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>135945181</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>135945183</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>135942929</v>
       </c>
       <c r="B23" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>135942930</v>
       </c>
       <c r="B24" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>135942927</v>
       </c>
       <c r="B26" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>135942938</v>
       </c>
       <c r="B27" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>135942943</v>
       </c>
       <c r="B28" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135942947</v>
       </c>
       <c r="B29" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>135945187</v>
       </c>
       <c r="B30" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>135942948</v>
       </c>
       <c r="B31" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136007050</v>
       </c>
       <c r="B32" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135942946</v>
       </c>
       <c r="B33" t="n">
-        <v>58603</v>
+        <v>58604</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>135942942</v>
       </c>
       <c r="B38" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>135945182</v>
       </c>
       <c r="B39" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 33564-2026 artfynd.xlsx
+++ b/artfynd/A 33564-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135942928</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135942926</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135942931</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>135942932</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135942933</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>135942935</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135942941</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>135942949</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135942951</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>135942952</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>135945181</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>135945183</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>135942929</v>
       </c>
       <c r="B23" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>135942930</v>
       </c>
       <c r="B24" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>135942927</v>
       </c>
       <c r="B26" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>135942938</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>135942943</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135942947</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>135945187</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>135942948</v>
       </c>
       <c r="B31" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136007050</v>
       </c>
       <c r="B32" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135942946</v>
       </c>
       <c r="B33" t="n">
-        <v>58604</v>
+        <v>58608</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>135942942</v>
       </c>
       <c r="B38" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>135945182</v>
       </c>
       <c r="B39" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 33564-2026 artfynd.xlsx
+++ b/artfynd/A 33564-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135942928</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135942926</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135942931</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>135942932</v>
       </c>
       <c r="B12" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135942933</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>135942935</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135942941</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>135942949</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>135942951</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>135942952</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>135945181</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>135945183</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>135942929</v>
       </c>
       <c r="B23" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>135942930</v>
       </c>
       <c r="B24" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>135942927</v>
       </c>
       <c r="B26" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>135942938</v>
       </c>
       <c r="B27" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>135942943</v>
       </c>
       <c r="B28" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135942947</v>
       </c>
       <c r="B29" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>135945187</v>
       </c>
       <c r="B30" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>135942948</v>
       </c>
       <c r="B31" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136007050</v>
       </c>
       <c r="B32" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135942946</v>
       </c>
       <c r="B33" t="n">
-        <v>58608</v>
+        <v>58609</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>135942942</v>
       </c>
       <c r="B38" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>135945182</v>
       </c>
       <c r="B39" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
